--- a/Data/EXCEL/Transfer/salemon/20240711/6812-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6812-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C1CFBD5-9CB2-4B6F-BCC3-D998ED752FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13B0305F-6F47-4A98-B604-8B54372B29F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{7EAE0536-658B-4AA7-ABBA-97CE048AAAF5}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{D9EE70E6-4652-48A7-AA62-290BE558878C}"/>
   </bookViews>
   <sheets>
     <sheet name="6812-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,17 +1261,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{127A10DC-768F-41D4-B3C5-FAE874DAFAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83A550C-62C4-46EE-84A1-E644EFB9D705}">
   <dimension ref="A1:Q97"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1298,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1380,7 +1380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1419,7 +1419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>176.3</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>121.7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>141.4</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>139.30000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>1739.5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>-65.099999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>-68.5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>-70.2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>-71.599999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>-73.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>-77.900000000000006</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>-81.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>-81.099999999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>-82.7</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>-87.4</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>-89</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>-99.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>-39.9</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>-29.1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>-21.5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>-12.7</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>-3.78</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>-3.24</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>-2.71</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>65.8</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>107.2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>100.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>93.7</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>184.3</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>159.1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>270.8</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>270.8</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>295.2</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3804,242 +3804,242 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>44105</v>
       </c>
